--- a/experiment_results/combined_sweep/rtt_bursts_S3_atk5pct_wu300000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S3_atk5pct_wu300000.xlsx
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00:009.9</t>
+          <t>00:010.1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,12 +516,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -533,27 +533,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00:020.1</t>
+          <t>00:019.9</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8.46</t>
+          <t>14.48</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,12 +573,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44951</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -590,27 +590,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:029.9</t>
+          <t>00:030.0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,12 +630,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>75681</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -652,22 +652,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>12.38</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>108190</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -709,22 +709,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -744,17 +744,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>209226</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
@@ -766,22 +766,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>107.2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -801,44 +801,44 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>371875</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:009.8</t>
+          <t>01:010.1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>103.6</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -858,17 +858,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>473238</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
@@ -880,22 +880,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>452897</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -932,27 +932,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01:029.8</t>
+          <t>01:030.0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>9.18</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>449128</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -989,27 +989,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01:040.2</t>
+          <t>01:040.0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>482137</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1051,22 +1051,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>503762</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1108,22 +1108,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>8.53</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>517374</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1165,22 +1165,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>533166</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1217,27 +1217,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02:019.9</t>
+          <t>02:020.1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>528739</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1274,27 +1274,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02:030.2</t>
+          <t>02:030.0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>10.33</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>546589</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1331,27 +1331,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02:039.7</t>
+          <t>02:039.9</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>549018</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1388,27 +1388,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02:050.1</t>
+          <t>02:050.2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>35.1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>508296</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1445,22 +1445,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02:055.0</t>
+          <t>02:055.2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1475,22 +1475,22 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>489748</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">

--- a/experiment_results/combined_sweep/rtt_bursts_S3_atk5pct_wu300000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S3_atk5pct_wu300000.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00:010.1</t>
+          <t>00:009.9</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,12 +516,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -533,27 +533,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00:019.9</t>
+          <t>00:020.3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>14.48</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>44951</t>
+          <t>19518</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -595,22 +595,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>75681</t>
+          <t>108125</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
@@ -652,22 +652,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>12.38</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>108190</t>
+          <t>174823</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -704,27 +704,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00:050.2</t>
+          <t>00:049.8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>209226</t>
+          <t>184294</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -754,34 +754,34 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00:059.8</t>
+          <t>01:000.0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>107.2</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>371875</t>
+          <t>184611</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -811,34 +811,34 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:010.1</t>
+          <t>01:010.0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>103.6</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>8.74</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>473238</t>
+          <t>190455</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -868,34 +868,34 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01:020.0</t>
+          <t>01:020.1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,17 +905,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>452897</t>
+          <t>202194</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -932,17 +932,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01:030.0</t>
+          <t>01:030.2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>449128</t>
+          <t>185128</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -994,22 +994,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>482137</t>
+          <t>180888</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1046,27 +1046,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01:050.0</t>
+          <t>01:050.2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>8.18</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>503762</t>
+          <t>182150</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1108,22 +1108,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>517374</t>
+          <t>166735</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1160,27 +1160,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02:010.2</t>
+          <t>02:010.0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>16.40</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>533166</t>
+          <t>157687</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1222,22 +1222,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>14.33</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>528739</t>
+          <t>155779</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1279,22 +1279,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>10.33</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>546589</t>
+          <t>140014</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1336,22 +1336,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>549018</t>
+          <t>103904</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1388,27 +1388,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02:050.2</t>
+          <t>02:050.0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1418,17 +1418,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>508296</t>
+          <t>51620</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1445,27 +1445,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02:055.2</t>
+          <t>02:055.1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1475,17 +1475,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>489748</t>
+          <t>21424</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1494,6 +1494,63 @@
         </is>
       </c>
       <c r="K19" t="inlineStr">
+        <is>
+          <t>Normal/Residual</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>03:000.2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>34.7</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>20.1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20760</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>Normal/Residual</t>
         </is>
